--- a/LoanOfficer-A/2023/71 Joychandra.xlsx
+++ b/LoanOfficer-A/2023/71 Joychandra.xlsx
@@ -605,7 +605,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -807,7 +807,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -816,7 +816,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>9600</v>
+        <v>10400</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -854,7 +854,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>14400</v>
+        <v>13600</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -1558,9 +1558,15 @@
       <c r="E21" s="1">
         <v>49</v>
       </c>
-      <c r="F21" s="3"/>
-      <c r="G21" s="4"/>
-      <c r="H21" s="1"/>
+      <c r="F21" s="3">
+        <v>45650</v>
+      </c>
+      <c r="G21" s="4">
+        <v>200</v>
+      </c>
+      <c r="H21" s="1">
+        <v>1</v>
+      </c>
       <c r="I21" s="1">
         <v>79</v>
       </c>
@@ -1590,9 +1596,15 @@
       <c r="E22" s="1">
         <v>50</v>
       </c>
-      <c r="F22" s="3"/>
-      <c r="G22" s="4"/>
-      <c r="H22" s="1"/>
+      <c r="F22" s="3">
+        <v>45651</v>
+      </c>
+      <c r="G22" s="4">
+        <v>200</v>
+      </c>
+      <c r="H22" s="1">
+        <v>1</v>
+      </c>
       <c r="I22" s="1">
         <v>80</v>
       </c>
@@ -1622,9 +1634,15 @@
       <c r="E23" s="1">
         <v>51</v>
       </c>
-      <c r="F23" s="3"/>
-      <c r="G23" s="4"/>
-      <c r="H23" s="1"/>
+      <c r="F23" s="3">
+        <v>45652</v>
+      </c>
+      <c r="G23" s="4">
+        <v>200</v>
+      </c>
+      <c r="H23" s="1">
+        <v>1</v>
+      </c>
       <c r="I23" s="1">
         <v>81</v>
       </c>
@@ -1654,9 +1672,15 @@
       <c r="E24" s="1">
         <v>52</v>
       </c>
-      <c r="F24" s="3"/>
-      <c r="G24" s="4"/>
-      <c r="H24" s="1"/>
+      <c r="F24" s="3">
+        <v>45653</v>
+      </c>
+      <c r="G24" s="4">
+        <v>200</v>
+      </c>
+      <c r="H24" s="1">
+        <v>1</v>
+      </c>
       <c r="I24" s="1">
         <v>82</v>
       </c>

--- a/LoanOfficer-A/2023/71 Joychandra.xlsx
+++ b/LoanOfficer-A/2023/71 Joychandra.xlsx
@@ -807,7 +807,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -816,7 +816,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>10400</v>
+        <v>12400</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -854,7 +854,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>13600</v>
+        <v>11600</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -886,9 +886,15 @@
       <c r="I3" s="1">
         <v>61</v>
       </c>
-      <c r="J3" s="3"/>
-      <c r="K3" s="4"/>
-      <c r="L3" s="1"/>
+      <c r="J3" s="3">
+        <v>45666</v>
+      </c>
+      <c r="K3" s="4">
+        <v>200</v>
+      </c>
+      <c r="L3" s="1">
+        <v>1</v>
+      </c>
       <c r="M3" s="1">
         <v>91</v>
       </c>
@@ -924,9 +930,15 @@
       <c r="I4" s="1">
         <v>62</v>
       </c>
-      <c r="J4" s="3"/>
-      <c r="K4" s="4"/>
-      <c r="L4" s="1"/>
+      <c r="J4" s="3">
+        <v>45667</v>
+      </c>
+      <c r="K4" s="4">
+        <v>200</v>
+      </c>
+      <c r="L4" s="1">
+        <v>1</v>
+      </c>
       <c r="M4" s="1">
         <v>92</v>
       </c>
@@ -1710,9 +1722,15 @@
       <c r="E25" s="1">
         <v>53</v>
       </c>
-      <c r="F25" s="3"/>
-      <c r="G25" s="4"/>
-      <c r="H25" s="1"/>
+      <c r="F25" s="3">
+        <v>45655</v>
+      </c>
+      <c r="G25" s="4">
+        <v>200</v>
+      </c>
+      <c r="H25" s="1">
+        <v>1</v>
+      </c>
       <c r="I25" s="1">
         <v>83</v>
       </c>
@@ -1742,9 +1760,15 @@
       <c r="E26" s="1">
         <v>54</v>
       </c>
-      <c r="F26" s="3"/>
-      <c r="G26" s="4"/>
-      <c r="H26" s="1"/>
+      <c r="F26" s="3">
+        <v>45656</v>
+      </c>
+      <c r="G26" s="4">
+        <v>200</v>
+      </c>
+      <c r="H26" s="1">
+        <v>1</v>
+      </c>
       <c r="I26" s="1">
         <v>84</v>
       </c>
@@ -1774,9 +1798,15 @@
       <c r="E27" s="1">
         <v>55</v>
       </c>
-      <c r="F27" s="3"/>
-      <c r="G27" s="4"/>
-      <c r="H27" s="1"/>
+      <c r="F27" s="3">
+        <v>45659</v>
+      </c>
+      <c r="G27" s="4">
+        <v>200</v>
+      </c>
+      <c r="H27" s="1">
+        <v>1</v>
+      </c>
       <c r="I27" s="1">
         <v>85</v>
       </c>
@@ -1806,9 +1836,15 @@
       <c r="E28" s="1">
         <v>56</v>
       </c>
-      <c r="F28" s="3"/>
-      <c r="G28" s="4"/>
-      <c r="H28" s="1"/>
+      <c r="F28" s="3">
+        <v>45660</v>
+      </c>
+      <c r="G28" s="4">
+        <v>200</v>
+      </c>
+      <c r="H28" s="1">
+        <v>1</v>
+      </c>
       <c r="I28" s="1">
         <v>86</v>
       </c>
@@ -1838,9 +1874,15 @@
       <c r="E29" s="1">
         <v>57</v>
       </c>
-      <c r="F29" s="3"/>
-      <c r="G29" s="4"/>
-      <c r="H29" s="1"/>
+      <c r="F29" s="3">
+        <v>45661</v>
+      </c>
+      <c r="G29" s="4">
+        <v>200</v>
+      </c>
+      <c r="H29" s="1">
+        <v>1</v>
+      </c>
       <c r="I29" s="1">
         <v>87</v>
       </c>
@@ -1870,9 +1912,15 @@
       <c r="E30" s="1">
         <v>58</v>
       </c>
-      <c r="F30" s="3"/>
-      <c r="G30" s="4"/>
-      <c r="H30" s="1"/>
+      <c r="F30" s="3">
+        <v>45662</v>
+      </c>
+      <c r="G30" s="4">
+        <v>200</v>
+      </c>
+      <c r="H30" s="1">
+        <v>1</v>
+      </c>
       <c r="I30" s="1">
         <v>88</v>
       </c>
@@ -1902,9 +1950,15 @@
       <c r="E31" s="1">
         <v>59</v>
       </c>
-      <c r="F31" s="3"/>
-      <c r="G31" s="4"/>
-      <c r="H31" s="1"/>
+      <c r="F31" s="3">
+        <v>45664</v>
+      </c>
+      <c r="G31" s="4">
+        <v>200</v>
+      </c>
+      <c r="H31" s="1">
+        <v>1</v>
+      </c>
       <c r="I31" s="1">
         <v>89</v>
       </c>
@@ -1934,9 +1988,15 @@
       <c r="E32" s="1">
         <v>60</v>
       </c>
-      <c r="F32" s="3"/>
-      <c r="G32" s="4"/>
-      <c r="H32" s="1"/>
+      <c r="F32" s="3">
+        <v>45665</v>
+      </c>
+      <c r="G32" s="4">
+        <v>200</v>
+      </c>
+      <c r="H32" s="1">
+        <v>1</v>
+      </c>
       <c r="I32" s="1">
         <v>90</v>
       </c>

--- a/LoanOfficer-A/2023/71 Joychandra.xlsx
+++ b/LoanOfficer-A/2023/71 Joychandra.xlsx
@@ -605,7 +605,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -807,7 +807,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -816,7 +816,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>12400</v>
+        <v>12800</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -854,7 +854,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>11600</v>
+        <v>11200</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -974,9 +974,15 @@
       <c r="I5" s="1">
         <v>63</v>
       </c>
-      <c r="J5" s="3"/>
-      <c r="K5" s="4"/>
-      <c r="L5" s="1"/>
+      <c r="J5" s="3">
+        <v>45671</v>
+      </c>
+      <c r="K5" s="4">
+        <v>200</v>
+      </c>
+      <c r="L5" s="1">
+        <v>1</v>
+      </c>
       <c r="M5" s="1">
         <v>93</v>
       </c>
@@ -1012,9 +1018,15 @@
       <c r="I6" s="1">
         <v>64</v>
       </c>
-      <c r="J6" s="3"/>
-      <c r="K6" s="4"/>
-      <c r="L6" s="1"/>
+      <c r="J6" s="3">
+        <v>45671</v>
+      </c>
+      <c r="K6" s="4">
+        <v>200</v>
+      </c>
+      <c r="L6" s="1">
+        <v>1</v>
+      </c>
       <c r="M6" s="1">
         <v>94</v>
       </c>

--- a/LoanOfficer-A/2023/71 Joychandra.xlsx
+++ b/LoanOfficer-A/2023/71 Joychandra.xlsx
@@ -605,7 +605,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -807,7 +807,7 @@
       </c>
       <c r="K1" s="10">
         <f>G1-K2</f>
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="L1" s="6"/>
       <c r="M1" s="5"/>
@@ -816,7 +816,7 @@
       </c>
       <c r="O1" s="8">
         <f>SUM(C3:C32)+SUM(G3:G32)+SUM(K3:K32)+SUM(O3:O32)</f>
-        <v>12800</v>
+        <v>24000</v>
       </c>
       <c r="P1" s="6"/>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="K2" s="9">
         <f>SUM(D3:D32)+SUM(H3:H32)+SUM(L3:L32)+SUM(P3:P32)</f>
-        <v>64</v>
+        <v>120</v>
       </c>
       <c r="L2" s="6"/>
       <c r="M2" s="5"/>
@@ -854,7 +854,7 @@
       </c>
       <c r="O2" s="11">
         <f>C2-O1</f>
-        <v>11200</v>
+        <v>0</v>
       </c>
       <c r="P2" s="6"/>
     </row>
@@ -898,9 +898,15 @@
       <c r="M3" s="1">
         <v>91</v>
       </c>
-      <c r="N3" s="3"/>
-      <c r="O3" s="4"/>
-      <c r="P3" s="1"/>
+      <c r="N3" s="3">
+        <v>45683</v>
+      </c>
+      <c r="O3" s="4">
+        <v>200</v>
+      </c>
+      <c r="P3" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="4" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
@@ -942,9 +948,15 @@
       <c r="M4" s="1">
         <v>92</v>
       </c>
-      <c r="N4" s="3"/>
-      <c r="O4" s="4"/>
-      <c r="P4" s="1"/>
+      <c r="N4" s="3">
+        <v>45683</v>
+      </c>
+      <c r="O4" s="4">
+        <v>200</v>
+      </c>
+      <c r="P4" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="5" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
@@ -986,9 +998,15 @@
       <c r="M5" s="1">
         <v>93</v>
       </c>
-      <c r="N5" s="3"/>
-      <c r="O5" s="4"/>
-      <c r="P5" s="1"/>
+      <c r="N5" s="3">
+        <v>45683</v>
+      </c>
+      <c r="O5" s="4">
+        <v>200</v>
+      </c>
+      <c r="P5" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="6" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
@@ -1030,9 +1048,15 @@
       <c r="M6" s="1">
         <v>94</v>
       </c>
-      <c r="N6" s="3"/>
-      <c r="O6" s="4"/>
-      <c r="P6" s="1"/>
+      <c r="N6" s="3">
+        <v>45683</v>
+      </c>
+      <c r="O6" s="4">
+        <v>200</v>
+      </c>
+      <c r="P6" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="7" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
@@ -1062,15 +1086,27 @@
       <c r="I7" s="1">
         <v>65</v>
       </c>
-      <c r="J7" s="3"/>
-      <c r="K7" s="4"/>
-      <c r="L7" s="1"/>
+      <c r="J7" s="3">
+        <v>45683</v>
+      </c>
+      <c r="K7" s="4">
+        <v>200</v>
+      </c>
+      <c r="L7" s="1">
+        <v>1</v>
+      </c>
       <c r="M7" s="1">
         <v>95</v>
       </c>
-      <c r="N7" s="3"/>
-      <c r="O7" s="4"/>
-      <c r="P7" s="1"/>
+      <c r="N7" s="3">
+        <v>45683</v>
+      </c>
+      <c r="O7" s="4">
+        <v>200</v>
+      </c>
+      <c r="P7" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="8" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
@@ -1100,15 +1136,27 @@
       <c r="I8" s="1">
         <v>66</v>
       </c>
-      <c r="J8" s="3"/>
-      <c r="K8" s="4"/>
-      <c r="L8" s="1"/>
+      <c r="J8" s="3">
+        <v>45683</v>
+      </c>
+      <c r="K8" s="4">
+        <v>200</v>
+      </c>
+      <c r="L8" s="1">
+        <v>1</v>
+      </c>
       <c r="M8" s="1">
         <v>96</v>
       </c>
-      <c r="N8" s="3"/>
-      <c r="O8" s="4"/>
-      <c r="P8" s="1"/>
+      <c r="N8" s="3">
+        <v>45683</v>
+      </c>
+      <c r="O8" s="4">
+        <v>200</v>
+      </c>
+      <c r="P8" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="9" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
@@ -1138,15 +1186,27 @@
       <c r="I9" s="1">
         <v>67</v>
       </c>
-      <c r="J9" s="3"/>
-      <c r="K9" s="4"/>
-      <c r="L9" s="1"/>
+      <c r="J9" s="3">
+        <v>45683</v>
+      </c>
+      <c r="K9" s="4">
+        <v>200</v>
+      </c>
+      <c r="L9" s="1">
+        <v>1</v>
+      </c>
       <c r="M9" s="1">
         <v>97</v>
       </c>
-      <c r="N9" s="3"/>
-      <c r="O9" s="4"/>
-      <c r="P9" s="1"/>
+      <c r="N9" s="3">
+        <v>45683</v>
+      </c>
+      <c r="O9" s="4">
+        <v>200</v>
+      </c>
+      <c r="P9" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="10" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
@@ -1176,15 +1236,27 @@
       <c r="I10" s="1">
         <v>68</v>
       </c>
-      <c r="J10" s="3"/>
-      <c r="K10" s="4"/>
-      <c r="L10" s="1"/>
+      <c r="J10" s="3">
+        <v>45683</v>
+      </c>
+      <c r="K10" s="4">
+        <v>200</v>
+      </c>
+      <c r="L10" s="1">
+        <v>1</v>
+      </c>
       <c r="M10" s="1">
         <v>98</v>
       </c>
-      <c r="N10" s="3"/>
-      <c r="O10" s="4"/>
-      <c r="P10" s="1"/>
+      <c r="N10" s="3">
+        <v>45683</v>
+      </c>
+      <c r="O10" s="4">
+        <v>200</v>
+      </c>
+      <c r="P10" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="11" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
@@ -1214,15 +1286,27 @@
       <c r="I11" s="1">
         <v>69</v>
       </c>
-      <c r="J11" s="3"/>
-      <c r="K11" s="4"/>
-      <c r="L11" s="1"/>
+      <c r="J11" s="3">
+        <v>45683</v>
+      </c>
+      <c r="K11" s="4">
+        <v>200</v>
+      </c>
+      <c r="L11" s="1">
+        <v>1</v>
+      </c>
       <c r="M11" s="1">
         <v>99</v>
       </c>
-      <c r="N11" s="3"/>
-      <c r="O11" s="4"/>
-      <c r="P11" s="1"/>
+      <c r="N11" s="3">
+        <v>45683</v>
+      </c>
+      <c r="O11" s="4">
+        <v>200</v>
+      </c>
+      <c r="P11" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="12" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
@@ -1252,15 +1336,27 @@
       <c r="I12" s="1">
         <v>70</v>
       </c>
-      <c r="J12" s="3"/>
-      <c r="K12" s="4"/>
-      <c r="L12" s="1"/>
+      <c r="J12" s="3">
+        <v>45683</v>
+      </c>
+      <c r="K12" s="4">
+        <v>200</v>
+      </c>
+      <c r="L12" s="1">
+        <v>1</v>
+      </c>
       <c r="M12" s="1">
         <v>100</v>
       </c>
-      <c r="N12" s="3"/>
-      <c r="O12" s="4"/>
-      <c r="P12" s="1"/>
+      <c r="N12" s="3">
+        <v>45683</v>
+      </c>
+      <c r="O12" s="4">
+        <v>200</v>
+      </c>
+      <c r="P12" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="13" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
@@ -1290,15 +1386,27 @@
       <c r="I13" s="1">
         <v>71</v>
       </c>
-      <c r="J13" s="3"/>
-      <c r="K13" s="4"/>
-      <c r="L13" s="1"/>
+      <c r="J13" s="3">
+        <v>45683</v>
+      </c>
+      <c r="K13" s="4">
+        <v>200</v>
+      </c>
+      <c r="L13" s="1">
+        <v>1</v>
+      </c>
       <c r="M13" s="1">
         <v>101</v>
       </c>
-      <c r="N13" s="3"/>
-      <c r="O13" s="4"/>
-      <c r="P13" s="1"/>
+      <c r="N13" s="3">
+        <v>45683</v>
+      </c>
+      <c r="O13" s="4">
+        <v>200</v>
+      </c>
+      <c r="P13" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="14" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1">
@@ -1328,15 +1436,27 @@
       <c r="I14" s="1">
         <v>72</v>
       </c>
-      <c r="J14" s="3"/>
-      <c r="K14" s="4"/>
-      <c r="L14" s="1"/>
+      <c r="J14" s="3">
+        <v>45683</v>
+      </c>
+      <c r="K14" s="4">
+        <v>200</v>
+      </c>
+      <c r="L14" s="1">
+        <v>1</v>
+      </c>
       <c r="M14" s="1">
         <v>102</v>
       </c>
-      <c r="N14" s="3"/>
-      <c r="O14" s="4"/>
-      <c r="P14" s="1"/>
+      <c r="N14" s="3">
+        <v>45683</v>
+      </c>
+      <c r="O14" s="4">
+        <v>200</v>
+      </c>
+      <c r="P14" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="15" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
@@ -1366,15 +1486,27 @@
       <c r="I15" s="1">
         <v>73</v>
       </c>
-      <c r="J15" s="3"/>
-      <c r="K15" s="4"/>
-      <c r="L15" s="1"/>
+      <c r="J15" s="3">
+        <v>45683</v>
+      </c>
+      <c r="K15" s="4">
+        <v>200</v>
+      </c>
+      <c r="L15" s="1">
+        <v>1</v>
+      </c>
       <c r="M15" s="1">
         <v>103</v>
       </c>
-      <c r="N15" s="3"/>
-      <c r="O15" s="4"/>
-      <c r="P15" s="1"/>
+      <c r="N15" s="3">
+        <v>45683</v>
+      </c>
+      <c r="O15" s="4">
+        <v>200</v>
+      </c>
+      <c r="P15" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="16" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
@@ -1404,15 +1536,27 @@
       <c r="I16" s="1">
         <v>74</v>
       </c>
-      <c r="J16" s="3"/>
-      <c r="K16" s="4"/>
-      <c r="L16" s="1"/>
+      <c r="J16" s="3">
+        <v>45683</v>
+      </c>
+      <c r="K16" s="4">
+        <v>200</v>
+      </c>
+      <c r="L16" s="1">
+        <v>1</v>
+      </c>
       <c r="M16" s="1">
         <v>104</v>
       </c>
-      <c r="N16" s="3"/>
-      <c r="O16" s="4"/>
-      <c r="P16" s="1"/>
+      <c r="N16" s="3">
+        <v>45683</v>
+      </c>
+      <c r="O16" s="4">
+        <v>200</v>
+      </c>
+      <c r="P16" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="17" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1">
@@ -1442,15 +1586,27 @@
       <c r="I17" s="1">
         <v>75</v>
       </c>
-      <c r="J17" s="3"/>
-      <c r="K17" s="4"/>
-      <c r="L17" s="1"/>
+      <c r="J17" s="3">
+        <v>45683</v>
+      </c>
+      <c r="K17" s="4">
+        <v>200</v>
+      </c>
+      <c r="L17" s="1">
+        <v>1</v>
+      </c>
       <c r="M17" s="1">
         <v>105</v>
       </c>
-      <c r="N17" s="3"/>
-      <c r="O17" s="4"/>
-      <c r="P17" s="1"/>
+      <c r="N17" s="3">
+        <v>45683</v>
+      </c>
+      <c r="O17" s="4">
+        <v>200</v>
+      </c>
+      <c r="P17" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="18" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1">
@@ -1480,15 +1636,27 @@
       <c r="I18" s="1">
         <v>76</v>
       </c>
-      <c r="J18" s="3"/>
-      <c r="K18" s="4"/>
-      <c r="L18" s="1"/>
+      <c r="J18" s="3">
+        <v>45683</v>
+      </c>
+      <c r="K18" s="4">
+        <v>200</v>
+      </c>
+      <c r="L18" s="1">
+        <v>1</v>
+      </c>
       <c r="M18" s="1">
         <v>106</v>
       </c>
-      <c r="N18" s="3"/>
-      <c r="O18" s="4"/>
-      <c r="P18" s="1"/>
+      <c r="N18" s="3">
+        <v>45683</v>
+      </c>
+      <c r="O18" s="4">
+        <v>200</v>
+      </c>
+      <c r="P18" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="19" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1">
@@ -1518,15 +1686,27 @@
       <c r="I19" s="1">
         <v>77</v>
       </c>
-      <c r="J19" s="3"/>
-      <c r="K19" s="4"/>
-      <c r="L19" s="1"/>
+      <c r="J19" s="3">
+        <v>45683</v>
+      </c>
+      <c r="K19" s="4">
+        <v>200</v>
+      </c>
+      <c r="L19" s="1">
+        <v>1</v>
+      </c>
       <c r="M19" s="1">
         <v>107</v>
       </c>
-      <c r="N19" s="3"/>
-      <c r="O19" s="4"/>
-      <c r="P19" s="1"/>
+      <c r="N19" s="3">
+        <v>45683</v>
+      </c>
+      <c r="O19" s="4">
+        <v>200</v>
+      </c>
+      <c r="P19" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="20" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1">
@@ -1556,15 +1736,27 @@
       <c r="I20" s="1">
         <v>78</v>
       </c>
-      <c r="J20" s="3"/>
-      <c r="K20" s="4"/>
-      <c r="L20" s="1"/>
+      <c r="J20" s="3">
+        <v>45683</v>
+      </c>
+      <c r="K20" s="4">
+        <v>200</v>
+      </c>
+      <c r="L20" s="1">
+        <v>1</v>
+      </c>
       <c r="M20" s="1">
         <v>108</v>
       </c>
-      <c r="N20" s="3"/>
-      <c r="O20" s="4"/>
-      <c r="P20" s="1"/>
+      <c r="N20" s="3">
+        <v>45683</v>
+      </c>
+      <c r="O20" s="4">
+        <v>200</v>
+      </c>
+      <c r="P20" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="21" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1">
@@ -1594,15 +1786,27 @@
       <c r="I21" s="1">
         <v>79</v>
       </c>
-      <c r="J21" s="3"/>
-      <c r="K21" s="4"/>
-      <c r="L21" s="1"/>
+      <c r="J21" s="3">
+        <v>45683</v>
+      </c>
+      <c r="K21" s="4">
+        <v>200</v>
+      </c>
+      <c r="L21" s="1">
+        <v>1</v>
+      </c>
       <c r="M21" s="1">
         <v>109</v>
       </c>
-      <c r="N21" s="3"/>
-      <c r="O21" s="4"/>
-      <c r="P21" s="1"/>
+      <c r="N21" s="3">
+        <v>45683</v>
+      </c>
+      <c r="O21" s="4">
+        <v>200</v>
+      </c>
+      <c r="P21" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="22" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1">
@@ -1632,15 +1836,27 @@
       <c r="I22" s="1">
         <v>80</v>
       </c>
-      <c r="J22" s="3"/>
-      <c r="K22" s="4"/>
-      <c r="L22" s="1"/>
+      <c r="J22" s="3">
+        <v>45683</v>
+      </c>
+      <c r="K22" s="4">
+        <v>200</v>
+      </c>
+      <c r="L22" s="1">
+        <v>1</v>
+      </c>
       <c r="M22" s="1">
         <v>110</v>
       </c>
-      <c r="N22" s="3"/>
-      <c r="O22" s="4"/>
-      <c r="P22" s="1"/>
+      <c r="N22" s="3">
+        <v>45683</v>
+      </c>
+      <c r="O22" s="4">
+        <v>200</v>
+      </c>
+      <c r="P22" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="23" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1">
@@ -1670,15 +1886,27 @@
       <c r="I23" s="1">
         <v>81</v>
       </c>
-      <c r="J23" s="3"/>
-      <c r="K23" s="4"/>
-      <c r="L23" s="1"/>
+      <c r="J23" s="3">
+        <v>45683</v>
+      </c>
+      <c r="K23" s="4">
+        <v>200</v>
+      </c>
+      <c r="L23" s="1">
+        <v>1</v>
+      </c>
       <c r="M23" s="1">
         <v>111</v>
       </c>
-      <c r="N23" s="3"/>
-      <c r="O23" s="4"/>
-      <c r="P23" s="1"/>
+      <c r="N23" s="3">
+        <v>45683</v>
+      </c>
+      <c r="O23" s="4">
+        <v>200</v>
+      </c>
+      <c r="P23" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="24" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
@@ -1708,15 +1936,27 @@
       <c r="I24" s="1">
         <v>82</v>
       </c>
-      <c r="J24" s="3"/>
-      <c r="K24" s="4"/>
-      <c r="L24" s="1"/>
+      <c r="J24" s="3">
+        <v>45683</v>
+      </c>
+      <c r="K24" s="4">
+        <v>200</v>
+      </c>
+      <c r="L24" s="1">
+        <v>1</v>
+      </c>
       <c r="M24" s="1">
         <v>112</v>
       </c>
-      <c r="N24" s="3"/>
-      <c r="O24" s="4"/>
-      <c r="P24" s="1"/>
+      <c r="N24" s="3">
+        <v>45683</v>
+      </c>
+      <c r="O24" s="4">
+        <v>200</v>
+      </c>
+      <c r="P24" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="25" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1">
@@ -1746,15 +1986,27 @@
       <c r="I25" s="1">
         <v>83</v>
       </c>
-      <c r="J25" s="3"/>
-      <c r="K25" s="4"/>
-      <c r="L25" s="1"/>
+      <c r="J25" s="3">
+        <v>45683</v>
+      </c>
+      <c r="K25" s="4">
+        <v>200</v>
+      </c>
+      <c r="L25" s="1">
+        <v>1</v>
+      </c>
       <c r="M25" s="1">
         <v>113</v>
       </c>
-      <c r="N25" s="3"/>
-      <c r="O25" s="4"/>
-      <c r="P25" s="1"/>
+      <c r="N25" s="3">
+        <v>45683</v>
+      </c>
+      <c r="O25" s="4">
+        <v>200</v>
+      </c>
+      <c r="P25" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="26" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1">
@@ -1784,15 +2036,27 @@
       <c r="I26" s="1">
         <v>84</v>
       </c>
-      <c r="J26" s="3"/>
-      <c r="K26" s="4"/>
-      <c r="L26" s="1"/>
+      <c r="J26" s="3">
+        <v>45683</v>
+      </c>
+      <c r="K26" s="4">
+        <v>200</v>
+      </c>
+      <c r="L26" s="1">
+        <v>1</v>
+      </c>
       <c r="M26" s="1">
         <v>114</v>
       </c>
-      <c r="N26" s="3"/>
-      <c r="O26" s="4"/>
-      <c r="P26" s="1"/>
+      <c r="N26" s="3">
+        <v>45683</v>
+      </c>
+      <c r="O26" s="4">
+        <v>200</v>
+      </c>
+      <c r="P26" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="27" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1">
@@ -1822,15 +2086,27 @@
       <c r="I27" s="1">
         <v>85</v>
       </c>
-      <c r="J27" s="3"/>
-      <c r="K27" s="4"/>
-      <c r="L27" s="1"/>
+      <c r="J27" s="3">
+        <v>45683</v>
+      </c>
+      <c r="K27" s="4">
+        <v>200</v>
+      </c>
+      <c r="L27" s="1">
+        <v>1</v>
+      </c>
       <c r="M27" s="1">
         <v>115</v>
       </c>
-      <c r="N27" s="3"/>
-      <c r="O27" s="4"/>
-      <c r="P27" s="1"/>
+      <c r="N27" s="3">
+        <v>45683</v>
+      </c>
+      <c r="O27" s="4">
+        <v>200</v>
+      </c>
+      <c r="P27" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="28" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1">
@@ -1860,15 +2136,27 @@
       <c r="I28" s="1">
         <v>86</v>
       </c>
-      <c r="J28" s="3"/>
-      <c r="K28" s="4"/>
-      <c r="L28" s="1"/>
+      <c r="J28" s="3">
+        <v>45683</v>
+      </c>
+      <c r="K28" s="4">
+        <v>200</v>
+      </c>
+      <c r="L28" s="1">
+        <v>1</v>
+      </c>
       <c r="M28" s="1">
         <v>116</v>
       </c>
-      <c r="N28" s="3"/>
-      <c r="O28" s="4"/>
-      <c r="P28" s="1"/>
+      <c r="N28" s="3">
+        <v>45683</v>
+      </c>
+      <c r="O28" s="4">
+        <v>200</v>
+      </c>
+      <c r="P28" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="29" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1">
@@ -1898,15 +2186,27 @@
       <c r="I29" s="1">
         <v>87</v>
       </c>
-      <c r="J29" s="3"/>
-      <c r="K29" s="4"/>
-      <c r="L29" s="1"/>
+      <c r="J29" s="3">
+        <v>45683</v>
+      </c>
+      <c r="K29" s="4">
+        <v>200</v>
+      </c>
+      <c r="L29" s="1">
+        <v>1</v>
+      </c>
       <c r="M29" s="1">
         <v>117</v>
       </c>
-      <c r="N29" s="3"/>
-      <c r="O29" s="4"/>
-      <c r="P29" s="1"/>
+      <c r="N29" s="3">
+        <v>45683</v>
+      </c>
+      <c r="O29" s="4">
+        <v>200</v>
+      </c>
+      <c r="P29" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="30" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1">
@@ -1936,15 +2236,27 @@
       <c r="I30" s="1">
         <v>88</v>
       </c>
-      <c r="J30" s="3"/>
-      <c r="K30" s="4"/>
-      <c r="L30" s="1"/>
+      <c r="J30" s="3">
+        <v>45683</v>
+      </c>
+      <c r="K30" s="4">
+        <v>200</v>
+      </c>
+      <c r="L30" s="1">
+        <v>1</v>
+      </c>
       <c r="M30" s="1">
         <v>118</v>
       </c>
-      <c r="N30" s="3"/>
-      <c r="O30" s="4"/>
-      <c r="P30" s="1"/>
+      <c r="N30" s="3">
+        <v>45683</v>
+      </c>
+      <c r="O30" s="4">
+        <v>200</v>
+      </c>
+      <c r="P30" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="31" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1">
@@ -1974,15 +2286,27 @@
       <c r="I31" s="1">
         <v>89</v>
       </c>
-      <c r="J31" s="3"/>
-      <c r="K31" s="4"/>
-      <c r="L31" s="1"/>
+      <c r="J31" s="3">
+        <v>45683</v>
+      </c>
+      <c r="K31" s="4">
+        <v>200</v>
+      </c>
+      <c r="L31" s="1">
+        <v>1</v>
+      </c>
       <c r="M31" s="1">
         <v>119</v>
       </c>
-      <c r="N31" s="3"/>
-      <c r="O31" s="4"/>
-      <c r="P31" s="1"/>
+      <c r="N31" s="3">
+        <v>45683</v>
+      </c>
+      <c r="O31" s="4">
+        <v>200</v>
+      </c>
+      <c r="P31" s="1">
+        <v>1</v>
+      </c>
     </row>
     <row r="32" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
@@ -2012,15 +2336,27 @@
       <c r="I32" s="1">
         <v>90</v>
       </c>
-      <c r="J32" s="3"/>
-      <c r="K32" s="4"/>
-      <c r="L32" s="1"/>
+      <c r="J32" s="3">
+        <v>45683</v>
+      </c>
+      <c r="K32" s="4">
+        <v>200</v>
+      </c>
+      <c r="L32" s="1">
+        <v>1</v>
+      </c>
       <c r="M32" s="1">
         <v>120</v>
       </c>
-      <c r="N32" s="3"/>
-      <c r="O32" s="4"/>
-      <c r="P32" s="1"/>
+      <c r="N32" s="3">
+        <v>45683</v>
+      </c>
+      <c r="O32" s="4">
+        <v>200</v>
+      </c>
+      <c r="P32" s="1">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <printOptions horizontalCentered="1"/>
